--- a/quizzes/039_mass_media_communication_quiz--quizzes.xlsx
+++ b/quizzes/039_mass_media_communication_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'mass_media_refers_to_a_medium_that_reaches_a_large_audience.'}</t>
+          <t>mass_media_refers_to_a_medium_that_reaches_a_large_audience.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Mass media refers to a medium that reaches a large audience.'}</t>
+          <t>Mass media refers to a medium that reaches a large audience.</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'mass_media_refers_to_an_individualized_experience.'}</t>
+          <t>mass_media_refers_to_an_individualized_experience.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Mass media refers to an individualized experience.'}</t>
+          <t>Mass media refers to an individualized experience.</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'mass_media_refers_to_a_specific_group_of_people.'}</t>
+          <t>mass_media_refers_to_a_specific_group_of_people.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Mass media refers to a specific group of people.'}</t>
+          <t>Mass media refers to a specific group of people.</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'radio'}</t>
+          <t>radio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Radio'}</t>
+          <t>Radio</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'television'}</t>
+          <t>television</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Television'}</t>
+          <t>Television</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'newspapers'}</t>
+          <t>newspapers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Newspapers'}</t>
+          <t>Newspapers</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'internet'}</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'Internet'}</t>
+          <t>Internet</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'text':_'print_media'}</t>
+          <t>print_media</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'text': 'Print media'}</t>
+          <t>Print media</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'text':_'outdoor_advertising'}</t>
+          <t>outdoor_advertising</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'text': 'Outdoor advertising'}</t>
+          <t>Outdoor advertising</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'it_helps_to_raise_awareness_about_a_product_or_service.'}</t>
+          <t>it_helps_to_raise_awareness_about_a_product_or_service.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'It helps to raise awareness about a product or service.'}</t>
+          <t>It helps to raise awareness about a product or service.</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'it_helps_to_influence_opinions_and_attitudes.'}</t>
+          <t>it_helps_to_influence_opinions_and_attitudes.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'It helps to influence opinions and attitudes.'}</t>
+          <t>It helps to influence opinions and attitudes.</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'it_helps_to_promote_cultural_identity.'}</t>
+          <t>it_helps_to_promote_cultural_identity.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'It helps to promote cultural identity.'}</t>
+          <t>It helps to promote cultural identity.</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'it_helps_to_shape_public_policy.'}</t>
+          <t>it_helps_to_shape_public_policy.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'It helps to shape public policy.'}</t>
+          <t>It helps to shape public policy.</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'it_will_become_more_personalized.'}</t>
+          <t>it_will_become_more_personalized.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'It will become more personalized.'}</t>
+          <t>It will become more personalized.</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'it_will_become_more_interactive.'}</t>
+          <t>it_will_become_more_interactive.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'It will become more interactive.'}</t>
+          <t>It will become more interactive.</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'it_will_become_less_interactive.'}</t>
+          <t>it_will_become_less_interactive.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'It will become less interactive.'}</t>
+          <t>It will become less interactive.</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'it_will_disappear.'}</t>
+          <t>it_will_disappear.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'It will disappear.'}</t>
+          <t>It will disappear.</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'mass_media_helps_to_shape_opinions_and_attitudes.'}</t>
+          <t>mass_media_helps_to_shape_opinions_and_attitudes.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Mass media helps to shape opinions and attitudes.'}</t>
+          <t>Mass media helps to shape opinions and attitudes.</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'mass_media_influences_cultural_identity.'}</t>
+          <t>mass_media_influences_cultural_identity.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Mass media influences cultural identity.'}</t>
+          <t>Mass media influences cultural identity.</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'mass_media_promotes_cultural_homogenization.'}</t>
+          <t>mass_media_promotes_cultural_homogenization.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Mass media promotes cultural homogenization.'}</t>
+          <t>Mass media promotes cultural homogenization.</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'mass_media_is_a_threat_to_democracy.'}</t>
+          <t>mass_media_is_a_threat_to_democracy.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'Mass media is a threat to democracy.'}</t>
+          <t>Mass media is a threat to democracy.</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'mass_media_uses_social_media.'}</t>
+          <t>mass_media_uses_social_media.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Mass media uses social media.'}</t>
+          <t>Mass media uses social media.</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'mass_media_uses_search_engines.'}</t>
+          <t>mass_media_uses_search_engines.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Mass media uses search engines.'}</t>
+          <t>Mass media uses search engines.</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'mass_media_uses_online_video_platforms.'}</t>
+          <t>mass_media_uses_online_video_platforms.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Mass media uses online video platforms.'}</t>
+          <t>Mass media uses online video platforms.</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
